--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_723_Canary_Isl_Spain.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_723_Canary_Isl_Spain.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rfbd1695e6b2743e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R337be191532a420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R27826ae3248543c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R784ea57d3d834486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfed68ddea1f34019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R25c13b25eaf445d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R503a149a43964183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9b2702cf0d4044f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re251c29c891c44f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R30a9acdd264e45a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Reb7abcb5779c475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R98d8aa978c214d59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ723CommercialTable" displayName="EEZ723CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ723CommercialTable" displayName="EEZ723CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ723FunctionalTable" displayName="EEZ723FunctionalTable" ref="A1:O24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O24"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ723FunctionalTable" displayName="EEZ723FunctionalTable" ref="A1:E24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E24"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ723ValidationTable" displayName="EEZ723ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ723ValidationTable" displayName="EEZ723ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12352,7 +12306,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fd6a8f4b92c473e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc8e7877bde840d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12362,20 +12316,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12383,660 +12327,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>236.76354920530002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1526554249158805</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>142.12007398928915</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>236.76354920530002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>142.8843557754822</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$175,A2,'Species'!$U$2:$U$175))</x:f>
-        <x:v>33829.807199315976</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1526554249158805</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>142.12007398928915</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>33648.85313102394</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>180.9540682920342</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.00537771874683</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0053777187468299235</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>533.1660272556</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.251467834185755</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1784.2998303280162</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>533.1660272556</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2072.695897207815</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$175,A3,'Species'!$U$2:$U$175))</x:f>
-        <x:v>1105091.0372232723</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.251467834185755</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1784.2998303280162</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>951328.0519688297</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>153762.98525444255</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.161629823630472</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.16162982363047212</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>12.5386292688</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9226619290664453</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>83.6877571958651</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>12.5386292688</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>94.47621852600095</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$175,A4,'Species'!$U$2:$U$175))</x:f>
-        <x:v>1184.6022788156602</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9226619290664453</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>83.6877571958651</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1049.329761816302</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>135.27251699935823</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.128913256748968</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.12891325674896786</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.26276000010000006</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.211003957957449</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>162.5563570311554</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.26276000010000006</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>162.61827491833367</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$175,A5,'Species'!$U$2:$U$175))</x:f>
-        <x:v>42.72957793380319</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.211003957957449</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>162.5563570311554</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>42.713308389762034</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.016269544041158213</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.000380901050621</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00038090105062097844</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2339.4635702059004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1375126053454134</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>137.25007971009813</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2339.4635702059004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>146.60206231646313</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$175,A6,'Species'!$U$2:$U$175))</x:f>
-        <x:v>342970.1841064207</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1375126053454134</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>137.25007971009813</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>321091.5614896306</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>21878.62261679012</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0681382672135302</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.06813826721353021</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>37.766332579200004</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0066994394512467</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.155456247727377</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>37.766332579200004</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.641372765690035</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$175,A7,'Species'!$U$2:$U$175))</x:f>
-        <x:v>401.8856229682912</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0066994394512467</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.155456247727377</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>383.53433814518667</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>18.35128482310455</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0478478274249272</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04784782742492716</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>11253.844207102002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4776449268315184</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>300.3619580600988</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>11253.844207102002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>514.2226851160793</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$175,A8,'Species'!$U$2:$U$175))</x:f>
-        <x:v>5786981.986054026</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4776449268315184</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>300.3619580600988</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3380226.6817484573</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2406755.3043055683</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7120100309546842</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7120100309546842</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>51477.811037198386</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.3593249446668945</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>228.7309557456642</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>51477.811037198386</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>531.4221313195648</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$175,A9,'Species'!$U$2:$U$175))</x:f>
-        <x:v>27356448.05705378</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.3593249446668945</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>228.7309557456642</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>11774568.91823309</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>15581879.13882069</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.323350285435242</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.3233502854352421</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>729.3286917104998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5862860220047077</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>385.73231347620754</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>729.3286917104998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>419.21755921836973</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$175,A10,'Species'!$U$2:$U$175))</x:f>
-        <x:v>305747.3940068026</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5862860220047077</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>385.73231347620754</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>281325.6435380668</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>24421.750468735758</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0868095427121318</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08680954271213173</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>247.92162165989998</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.133678731073182</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1360.4379274856499</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>247.92162165989998</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1597.2963220146319</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$175,A11,'Species'!$U$2:$U$175))</x:f>
-        <x:v>396004.2944252613</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.133678731073182</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1360.4379274856499</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>337281.9771498757</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>58722.317275385605</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.174104521598234</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.174104521598234</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>25957.598633539495</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.401021078347967</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2517.7991253929854</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>25957.598633539495</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2565.4140255803254</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$175,A12,'Species'!$U$2:$U$175))</x:f>
-        <x:v>66591987.60486691</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.401021078347967</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2517.7991253929854</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>65356019.13682789</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1235968.4680390134</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0189113181060097</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.018911318106009756</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re066ec7602814fe5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c201c2028c45b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13046,20 +12561,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13067,1308 +12572,459 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>228.7540822761</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.034089540156363</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1081.6569376629616</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>228.7540822761</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1387.2077480811686</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$175,A2,'Species'!$U$2:$U$175))</x:f>
-        <x:v>317329.43533860304</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.034089540156363</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1081.6569376629616</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>247433.44011266748</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>69895.99522593556</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2824840296206883</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.2824840296206883</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>353.31904089980003</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.136166229828931</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1368.252435393316</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>353.31904089980003</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1371.7619858995884</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$175,A3,'Species'!$U$2:$U$175))</x:f>
-        <x:v>484669.6292008476</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.136166229828931</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1368.252435393316</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>483429.63818198204</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1239.9910188655485</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0025649875823268</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0025649875823268555</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7.683136702600001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.340000000000001</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.7616239495565</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7.683136702600001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$175,A4,'Species'!$U$2:$U$175))</x:f>
-        <x:v>16808.871629506582</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.340000000000001</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.7616239495565</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>16808.87162950662</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>-3.637978807091713e-11</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>0.9999999999999979</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>-2.1643206559478593e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1058.3426399624</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4060006262311124</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>254.6833924990652</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1058.3426399624</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>990.1772178520795</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$175,A5,'Species'!$U$2:$U$175))</x:f>
-        <x:v>1047946.7707721943</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4060006262311124</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>254.6833924990652</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>269542.29397204076</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>778404.4768001535</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>3.8878750912496733</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>2.8878750912496733</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2283.2021319650003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.041229970480255</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1099.5879463646363</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2283.2021319650003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1240.5090874072935</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$175,A6,'Species'!$U$2:$U$175))</x:f>
-        <x:v>2832332.993090289</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.041229970480255</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1099.5879463646363</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2510581.543422754</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>321751.44966753526</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1281581355166348</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1281581355166347</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>27316.273995886393</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.396006154499833</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2488.8925887753962</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>27316.273995886393</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2534.7467910825694</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$175,A7,'Species'!$U$2:$U$175))</x:f>
-        <x:v>69239837.85540527</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.396006154499833</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2488.8925887753962</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>67987271.90131973</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1252565.9540855438</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.018423536039269</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.018423536039268988</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>59.3505187856</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.028153841540833</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1066.9740119553414</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>59.3505187856</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1092.6394879967067</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$175,A8,'Species'!$U$2:$U$175))</x:f>
-        <x:v>64848.72045823691</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.028153841540833</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1066.9740119553414</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>63325.46114030249</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1523.2593179344185</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0240544528299529</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.02405445282995285</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3909.5267671627</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.29066810303617</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1952.84647907431</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3909.5267671627</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2180.204520732274</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$175,A9,'Species'!$U$2:$U$175))</x:f>
-        <x:v>8523567.93169195</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.29066810303617</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1952.84647907431</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>7634705.582100448</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>888862.349591502</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1164239196957952</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.11642391969579521</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>188.57110287429998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.1668914388692055</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1468.5591342082137</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>188.57110287429998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1756.1310769220565</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$175,A10,'Species'!$U$2:$U$175))</x:f>
-        <x:v>331155.57396702433</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.1668914388692055</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1468.5591342082137</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>276927.81557376997</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>54227.758393254364</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.195819110048224</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.19581911004822408</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.9938699998999999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1215315886405195</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>132.29139273599225</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.9938699998999999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>144.03687509748315</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$175,A11,'Species'!$U$2:$U$175))</x:f>
-        <x:v>143.1539290387319</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1215315886405195</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>132.29139273599225</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>131.48044648529145</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>11.673482553440437</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0887849324024492</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.08878493240244917</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>875.4844585202001</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6595259973752805</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>456.5895813701823</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>875.4844585202001</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>562.5486878829147</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$175,A12,'Species'!$U$2:$U$175))</x:f>
-        <x:v>492502.6334024226</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6595259973752805</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>456.5895813701823</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>399737.08241183887</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>92765.55099058372</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2320664133306747</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.23206641333067457</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>176.59149494629997</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.857331918505338</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>719.9990418796219</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>176.59149494629997</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>770.6825214777301</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$175,A13,'Species'!$U$2:$U$175))</x:f>
-        <x:v>136095.9785967363</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.857331918505338</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>719.9990418796219</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>127145.70716542608</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>8950.271431310219</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0703938153386905</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.07039381533869048</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>18875.917099458304</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.1306397888914965</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>135.09515965303657</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>18875.917099458304</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>301.9396442673561</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$175,A14,'Species'!$U$2:$U$175))</x:f>
-        <x:v>5699387.694230543</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.1306397888914965</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>135.09515965303657</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2550045.0341488025</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>3149342.660081741</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.235014526374034</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.2350145263740342</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>12918.678544912102</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.1247617829746006</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>133.27901762635958</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>12918.678544912102</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>175.56857398003152</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$175,A15,'Species'!$U$2:$U$175))</x:f>
-        <x:v>2268113.969836646</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.1247617829746006</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>133.27901762635958</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1721788.7854966132</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>546325.184340033</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3173009308354027</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.31730093083540273</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>7609.723921802799</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.7847624446709154</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>609.2035769940334</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>7609.723921802799</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>794.537280107157</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$175,A16,'Species'!$U$2:$U$175))</x:f>
-        <x:v>6046209.347195564</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.7847624446709154</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>609.2035769940334</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4635871.033099329</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1410338.3140962347</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.304222939772625</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.30422293977262516</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>6943.5033625363</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.940810037440875</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>87.2589609881993</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>6943.5033625363</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>103.58865254984684</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$175,A17,'Species'!$U$2:$U$175))</x:f>
-        <x:v>719268.1573004661</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.940810037440875</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>87.2589609881993</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>605882.8890329858</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>113385.2682674803</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1871405684495364</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.18714056844953633</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>39.8967445542</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.023052599591592</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.545146062312774</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>39.8967445542</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>11.301359459099292</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$175,A18,'Species'!$U$2:$U$175))</x:f>
-        <x:v>450.88745145487627</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.023052599591592</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.545146062312774</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>420.7169987348207</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>30.17045272005555</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.07171198884472</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.07171198884472002</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>11.5447592689</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.9055415557492257</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>80.4528726722331</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>11.5447592689</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>90.20962027181004</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$175,A19,'Species'!$U$2:$U$175))</x:f>
-        <x:v>1041.4483497769284</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.9055415557492257</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>80.4528726722331</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>928.8090474923946</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>112.63930228453376</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1212728306088728</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.1212728306088729</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>922.4393890099</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3961722189536876</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>248.98444673675618</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>922.4393890099</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>252.11400150106235</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$175,A20,'Species'!$U$2:$U$175))</x:f>
-        <x:v>232559.88550548095</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3961722189536876</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>248.98444673675618</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>229673.06092082136</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2886.8245846595964</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0125692781429634</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.012569278142963465</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>112.9325566219</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.47286366934101</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>297.07333337087186</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>112.9325566219</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>298.53596193805754</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$175,A21,'Species'!$U$2:$U$175))</x:f>
-        <x:v>33714.42942524307</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.47286366934101</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>297.07333337087186</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>33549.25104176256</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>165.1783834805101</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0049234596407202</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.00492345964072026</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2848.8493512654004</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.2577661839585086</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>181.03651633938796</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2848.8493512654004</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>221.79131556673218</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$175,A22,'Species'!$U$2:$U$175))</x:f>
-        <x:v>631850.0454685846</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.2577661839585086</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>181.03651633938796</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>515745.7621288134</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>116104.28333977121</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.2251192193233627</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.22511921932336273</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>6084.623330313999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.581543638386613</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>381.5431302262362</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>6084.623330313999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>460.3097494364003</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$175,A23,'Species'!$U$2:$U$175))</x:f>
-        <x:v>2800811.4405917125</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.581543638386613</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>381.5431302262362</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>2321546.231695589</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>479265.20889612334</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2064422419647798</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.2064422419647797</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>0.26276000010000006</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.211003957957449</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>162.5563570311554</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>0.26276000010000006</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>162.61827491833367</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$175,A24,'Species'!$U$2:$U$175))</x:f>
-        <x:v>42.72957793380319</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.211003957957449</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>162.5563570311554</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>42.713308389762034</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0.016269544041158213</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.000380901050621</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.00038090105062097844</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G24">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O24">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabf72a0ab3e34a56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1082393996b4c07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14543,7 +13199,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -14642,7 +13298,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>101920689.58241552</x:v>
+        <x:v>82436966.40149522</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14656,7 +13312,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>101920689.58241552</x:v>
+        <x:v>92632535.1043963</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14670,7 +13326,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-19483723.180920273</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14684,7 +13340,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-9288154.478019193</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -14695,9 +13351,9 @@
         <x:v>EEZ_723</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -14709,47 +13365,19 @@
         <x:v>EEZ_723</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_723</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_723</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4f0594fe7334fa8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72f9a6eefbd0490b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14796,7 +13424,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
